--- a/TodoList.xlsx
+++ b/TodoList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mikajy\Documents\GitHub\Mini-Projet-Web-Mars2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0654D015-2F60-44BE-B793-F7A2F353B4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8C48B9-5CFA-4296-B618-191CA9716182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="groupe" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId6"/>
+    <pivotCache cacheId="15" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="88">
   <si>
     <t>Ligne</t>
   </si>
@@ -157,6 +157,9 @@
     <t>Docker</t>
   </si>
   <si>
+    <t>Frontoffice</t>
+  </si>
+  <si>
     <t>Configuration</t>
   </si>
   <si>
@@ -260,6 +263,48 @@
   </si>
   <si>
     <t>Retourner JSON pour TinyMCE</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>Créer un page d'accueil</t>
+  </si>
+  <si>
+    <t>Recuperer et afficher les articles recents avec titre,section</t>
+  </si>
+  <si>
+    <t>Créer page article detail</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>Article</t>
+  </si>
+  <si>
+    <t>Recuperer article par slug</t>
+  </si>
+  <si>
+    <t>Afficher contenu formate</t>
+  </si>
+  <si>
+    <t>Gestion erreur(article inexistant)</t>
+  </si>
+  <si>
+    <t>Layout</t>
+  </si>
+  <si>
+    <t>layout</t>
+  </si>
+  <si>
+    <t>Créer template header/footer</t>
+  </si>
+  <si>
+    <t>Ajouter navigation cohérente</t>
   </si>
 </sst>
 </file>
@@ -633,7 +678,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Mikajy" refreshedDate="46111.802376157408" refreshedVersion="7" recordCount="112" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Mikajy" refreshedDate="46111.832195833333" refreshedVersion="7" recordCount="112" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K919" sheet="liste des taches"/>
   </cacheSource>
@@ -774,7 +819,7 @@
     <s v="Config"/>
     <s v="Créer fonction slugify pour url et escape pour protection"/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="10"/>
     <n v="10"/>
     <n v="0"/>
@@ -786,7 +831,7 @@
     <s v="index"/>
     <s v="Créer router principale et ajouter routes"/>
     <s v="Integration"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="20"/>
     <n v="20"/>
     <n v="0"/>
@@ -798,7 +843,7 @@
     <s v="dashboard"/>
     <s v="Liste articles"/>
     <s v="Affichage"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -810,7 +855,7 @@
     <s v="dashboard"/>
     <s v="Lien modifier/ supprimer par article"/>
     <s v="Integration"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="5"/>
     <n v="5"/>
     <n v="0"/>
@@ -822,7 +867,7 @@
     <s v="article_add"/>
     <s v="Formulaire ajout article,upload,title,categorie"/>
     <s v="Affichage"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="20"/>
     <n v="20"/>
     <n v="0"/>
@@ -834,7 +879,7 @@
     <s v="article_add"/>
     <s v="Integration TinyMCE"/>
     <s v="Integration"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -846,7 +891,7 @@
     <s v="article_add"/>
     <s v="Synchroniser TinyMCE -&gt; textarea"/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -858,7 +903,7 @@
     <s v="article_edit"/>
     <s v="Créer formulaire modification article"/>
     <s v="Affichage"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="15"/>
     <n v="15"/>
     <n v="0"/>
@@ -870,7 +915,7 @@
     <s v="article_edit"/>
     <s v="Pre remplir formulaire "/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="10"/>
     <n v="10"/>
     <n v="0"/>
@@ -882,7 +927,7 @@
     <s v="article_edit"/>
     <s v="Integration TinyMCE pour contenu"/>
     <s v="Integration"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="10"/>
     <n v="10"/>
     <n v="0"/>
@@ -894,7 +939,7 @@
     <s v="article_edit"/>
     <s v="Synchroniser TinyMCE -&gt; textarea"/>
     <s v="Metier"/>
-    <x v="2"/>
+    <x v="0"/>
     <n v="10"/>
     <n v="10"/>
     <n v="0"/>
@@ -961,100 +1006,100 @@
     <n v="1"/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <s v="Frontoffice"/>
+    <s v="Home"/>
+    <s v="home"/>
+    <s v="Créer un page d'accueil"/>
+    <s v="Affichage"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Home"/>
+    <s v="home"/>
+    <s v="Recuperer et afficher les articles recents avec titre,section"/>
+    <s v="Metier"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Article"/>
+    <s v="article"/>
+    <s v="Créer page article detail"/>
+    <s v="Affichage"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Article"/>
+    <s v="article"/>
+    <s v="Recuperer article par slug"/>
+    <s v="Metier"/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Article"/>
+    <s v="article"/>
+    <s v="Afficher contenu formate"/>
+    <s v="Affichage"/>
+    <x v="1"/>
+    <n v="15"/>
+    <n v="15"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Article"/>
+    <s v="article"/>
+    <s v="Gestion erreur(article inexistant)"/>
+    <s v="Metier"/>
+    <x v="1"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Layout"/>
+    <s v="layout"/>
+    <s v="Créer template header/footer"/>
+    <s v="Affichage"/>
+    <x v="1"/>
+    <n v="20"/>
+    <n v="20"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
-  </r>
-  <r>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="2"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+  </r>
+  <r>
+    <s v="Frontoffice"/>
+    <s v="Layout"/>
+    <s v="layout"/>
+    <s v="Ajouter navigation cohérente"/>
+    <s v="Affichage"/>
+    <x v="1"/>
+    <n v="10"/>
+    <n v="10"/>
     <n v="0"/>
-    <e v="#DIV/0!"/>
+    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -2056,7 +2101,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField name="Catégorie" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -2518,7 +2563,7 @@
         <v>36</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>15</v>
@@ -2555,7 +2600,7 @@
         <v>36</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>14</v>
@@ -2586,13 +2631,13 @@
         <v>15</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>15</v>
@@ -2623,13 +2668,13 @@
         <v>15</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>13</v>
@@ -2657,16 +2702,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>14</v>
@@ -2697,13 +2742,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="39" t="s">
         <v>12</v>
@@ -2734,13 +2779,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="42" t="s">
         <v>14</v>
@@ -2771,13 +2816,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="40" t="s">
         <v>12</v>
@@ -2808,13 +2853,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="40" t="s">
         <v>14</v>
@@ -2845,13 +2890,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="40" t="s">
         <v>13</v>
@@ -2882,13 +2927,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" s="40" t="s">
         <v>12</v>
@@ -2919,13 +2964,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="40" t="s">
         <v>13</v>
@@ -2956,13 +3001,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="40" t="s">
         <v>61</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>60</v>
       </c>
       <c r="F16" s="40" t="s">
         <v>14</v>
@@ -2993,13 +3038,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="40" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>56</v>
       </c>
       <c r="F17" s="40" t="s">
         <v>13</v>
@@ -3030,13 +3075,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="40" t="s">
         <v>14</v>
@@ -3067,16 +3112,16 @@
         <v>11</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>67</v>
       </c>
       <c r="G19" s="47" t="s">
         <v>31</v>
@@ -3104,13 +3149,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F20" s="40" t="s">
         <v>14</v>
@@ -3141,13 +3186,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="40" t="s">
         <v>13</v>
@@ -3178,13 +3223,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="40" t="s">
         <v>14</v>
@@ -3211,168 +3256,296 @@
       <c r="A23" s="45">
         <v>22</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="49"/>
+      <c r="B23" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="47">
+        <v>20</v>
+      </c>
+      <c r="I23" s="49">
+        <v>20</v>
+      </c>
       <c r="J23" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K23" s="6" t="e">
+      <c r="K23" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="45">
         <v>23</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="49"/>
+      <c r="B24" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="47">
+        <v>20</v>
+      </c>
+      <c r="I24" s="49">
+        <v>20</v>
+      </c>
       <c r="J24" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K24" s="6" t="e">
+      <c r="K24" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="45">
         <v>24</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="49"/>
+      <c r="B25" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="47">
+        <v>20</v>
+      </c>
+      <c r="I25" s="49">
+        <v>20</v>
+      </c>
       <c r="J25" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K25" s="6" t="e">
+      <c r="K25" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="45">
         <v>25</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="49"/>
+      <c r="B26" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="47">
+        <v>15</v>
+      </c>
+      <c r="I26" s="49">
+        <v>15</v>
+      </c>
       <c r="J26" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K26" s="6" t="e">
+      <c r="K26" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="45">
         <v>26</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="49"/>
+      <c r="B27" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="47">
+        <v>15</v>
+      </c>
+      <c r="I27" s="49">
+        <v>15</v>
+      </c>
       <c r="J27" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="6" t="e">
+      <c r="K27" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="45">
         <v>27</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="49"/>
+      <c r="B28" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="47">
+        <v>10</v>
+      </c>
+      <c r="I28" s="49">
+        <v>10</v>
+      </c>
       <c r="J28" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K28" s="6" t="e">
+      <c r="K28" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="45">
         <v>28</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="49"/>
+      <c r="B29" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="47">
+        <v>20</v>
+      </c>
+      <c r="I29" s="49">
+        <v>20</v>
+      </c>
       <c r="J29" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K29" s="6" t="e">
+      <c r="K29" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="45">
         <v>29</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="49"/>
+      <c r="B30" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="47">
+        <v>10</v>
+      </c>
+      <c r="I30" s="49">
+        <v>10</v>
+      </c>
       <c r="J30" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K30" s="6" t="e">
+      <c r="K30" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1">
@@ -4676,10 +4849,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="23">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="C3" s="24">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="D3" s="25">
         <v>0</v>
@@ -4690,10 +4863,10 @@
         <v>29</v>
       </c>
       <c r="B4" s="27">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="C4" s="28">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="D4" s="29">
         <v>0</v>
@@ -4703,12 +4876,8 @@
       <c r="A5" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="27">
-        <v>145</v>
-      </c>
-      <c r="C5" s="28">
-        <v>145</v>
-      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="29">
         <v>0</v>
       </c>
@@ -4718,10 +4887,10 @@
         <v>16</v>
       </c>
       <c r="B6" s="31">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="C6" s="32">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="D6" s="33">
         <v>0</v>
@@ -4777,11 +4946,11 @@
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="11">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="B2" s="11">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="C2" s="11">
         <f>SUM('liste des taches'!J:J)</f>
@@ -4829,17 +4998,11 @@
         <v>23</v>
       </c>
       <c r="C1" s="15">
-        <v>46048</v>
-      </c>
-      <c r="D1" s="15">
-        <v>46049</v>
-      </c>
-      <c r="E1" s="15">
-        <v>46056</v>
-      </c>
-      <c r="F1" s="15">
-        <v>46063</v>
-      </c>
+        <v>46111</v>
+      </c>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="16">
@@ -4888,10 +5051,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="16">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="16">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -4902,10 +5065,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
@@ -4916,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="16">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="16">
         <v>15</v>
@@ -4958,26 +5121,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C10" s="16">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="16">
-        <v>5</v>
-      </c>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="16">
         <v>10</v>
       </c>
       <c r="B11" s="16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C11" s="16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -4988,28 +5149,26 @@
         <v>11</v>
       </c>
       <c r="B12" s="16">
-        <v>20</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16">
-        <v>10</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C12" s="16">
+        <v>15</v>
+      </c>
+      <c r="D12" s="16"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="16">
-        <v>10</v>
-      </c>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="16">
         <v>12</v>
       </c>
       <c r="B13" s="16">
-        <v>20</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16">
-        <v>20</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C13" s="16">
+        <v>15</v>
+      </c>
+      <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="52"/>
     </row>
@@ -5020,10 +5179,10 @@
       <c r="B14" s="16">
         <v>15</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16">
-        <v>15</v>
-      </c>
+      <c r="C14" s="16">
+        <v>15</v>
+      </c>
+      <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="52"/>
     </row>
@@ -5034,10 +5193,10 @@
       <c r="B15" s="16">
         <v>10</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16">
+      <c r="C15" s="16">
         <v>10</v>
       </c>
+      <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="52"/>
     </row>
@@ -5046,32 +5205,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="16">
-        <v>20</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16">
         <v>10</v>
       </c>
+      <c r="C16" s="16">
+        <v>10</v>
+      </c>
+      <c r="D16" s="16"/>
       <c r="E16" s="16"/>
-      <c r="F16" s="16">
-        <v>10</v>
-      </c>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="16">
         <v>16</v>
       </c>
       <c r="B17" s="16">
-        <v>15</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16">
         <v>10</v>
       </c>
+      <c r="C17" s="16">
+        <v>10</v>
+      </c>
+      <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="16">
-        <v>5</v>
-      </c>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="16">
@@ -5080,10 +5235,10 @@
       <c r="B18" s="16">
         <v>15</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16">
-        <v>15</v>
-      </c>
+      <c r="C18" s="16">
+        <v>15</v>
+      </c>
+      <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="52"/>
     </row>
@@ -5092,12 +5247,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="16">
-        <v>10</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16">
-        <v>10</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C19" s="16">
+        <v>30</v>
+      </c>
+      <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="52"/>
     </row>
@@ -5108,10 +5263,10 @@
       <c r="B20" s="16">
         <v>20</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16">
+      <c r="C20" s="16">
         <v>20</v>
       </c>
+      <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="52"/>
     </row>
@@ -5120,12 +5275,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="16">
-        <v>15</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16">
-        <v>15</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C21" s="16">
+        <v>20</v>
+      </c>
+      <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="52"/>
     </row>
@@ -5134,28 +5289,26 @@
         <v>21</v>
       </c>
       <c r="B22" s="16">
-        <v>30</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16">
         <v>10</v>
       </c>
+      <c r="C22" s="16">
+        <v>10</v>
+      </c>
+      <c r="D22" s="16"/>
       <c r="E22" s="16"/>
-      <c r="F22" s="16">
-        <v>20</v>
-      </c>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="16">
         <v>22</v>
       </c>
       <c r="B23" s="16">
-        <v>10</v>
-      </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C23" s="16">
+        <v>20</v>
+      </c>
+      <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="52"/>
     </row>
@@ -5164,12 +5317,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="16">
-        <v>10</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C24" s="16">
+        <v>20</v>
+      </c>
+      <c r="D24" s="16"/>
       <c r="E24" s="16"/>
       <c r="F24" s="52"/>
     </row>
@@ -5178,12 +5331,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="16">
-        <v>15</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16">
-        <v>15</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C25" s="16">
+        <v>20</v>
+      </c>
+      <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="52"/>
     </row>
@@ -5192,60 +5345,54 @@
         <v>25</v>
       </c>
       <c r="B26" s="16">
-        <v>30</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16">
-        <v>20</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C26" s="16">
+        <v>15</v>
+      </c>
+      <c r="D26" s="16"/>
       <c r="E26" s="16"/>
-      <c r="F26" s="16">
-        <v>10</v>
-      </c>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="16">
         <v>26</v>
       </c>
       <c r="B27" s="16">
-        <v>20</v>
-      </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16">
-        <v>10</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C27" s="16">
+        <v>15</v>
+      </c>
+      <c r="D27" s="16"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="16">
-        <v>10</v>
-      </c>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="16">
         <v>27</v>
       </c>
       <c r="B28" s="16">
-        <v>30</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C28" s="16">
+        <v>10</v>
+      </c>
+      <c r="D28" s="16"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="16">
-        <v>15</v>
-      </c>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="16">
         <v>28</v>
       </c>
       <c r="B29" s="16">
-        <v>10</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C29" s="16">
+        <v>20</v>
+      </c>
+      <c r="D29" s="16"/>
       <c r="E29" s="16"/>
       <c r="F29" s="52"/>
     </row>
@@ -5254,66 +5401,50 @@
         <v>29</v>
       </c>
       <c r="B30" s="16">
-        <v>20</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16">
-        <v>15</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C30" s="16">
+        <v>10</v>
+      </c>
+      <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-      <c r="F30" s="16">
-        <v>5</v>
-      </c>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="16">
         <v>30</v>
       </c>
-      <c r="B31" s="16">
-        <v>10</v>
-      </c>
+      <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="16">
-        <v>10</v>
-      </c>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="16">
         <v>31</v>
       </c>
-      <c r="B32" s="16">
-        <v>10</v>
-      </c>
+      <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
-      <c r="F32" s="16">
-        <v>10</v>
-      </c>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
       <c r="A33" s="16">
         <v>32</v>
       </c>
-      <c r="B33" s="16">
-        <v>10</v>
-      </c>
+      <c r="B33" s="16"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="16">
-        <v>10</v>
-      </c>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">
       <c r="A34" s="16">
         <v>33</v>
       </c>
-      <c r="B34" s="16">
-        <v>10</v>
-      </c>
+      <c r="B34" s="16"/>
       <c r="C34" s="16">
         <v>10</v>
       </c>
@@ -5345,9 +5476,7 @@
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
-      <c r="F36" s="16">
-        <v>10</v>
-      </c>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
       <c r="A37" s="16">
@@ -5357,9 +5486,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="16"/>
-      <c r="D37" s="16">
-        <v>10</v>
-      </c>
+      <c r="D37" s="16"/>
       <c r="E37" s="16"/>
       <c r="F37" s="16"/>
     </row>
@@ -5371,13 +5498,9 @@
         <v>15</v>
       </c>
       <c r="C38" s="16"/>
-      <c r="D38" s="16">
-        <v>10</v>
-      </c>
+      <c r="D38" s="16"/>
       <c r="E38" s="16"/>
-      <c r="F38" s="16">
-        <v>5</v>
-      </c>
+      <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1">
       <c r="A39" s="16">
@@ -5388,12 +5511,8 @@
       </c>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
-      <c r="E39" s="16">
-        <v>15</v>
-      </c>
-      <c r="F39" s="16">
-        <v>5</v>
-      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1">
       <c r="A40" s="16">
@@ -5404,9 +5523,7 @@
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
-      <c r="E40" s="16">
-        <v>10</v>
-      </c>
+      <c r="E40" s="16"/>
       <c r="F40" s="52"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1">
@@ -5418,12 +5535,8 @@
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
-      <c r="E41" s="16">
-        <v>15</v>
-      </c>
-      <c r="F41" s="16">
-        <v>10</v>
-      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1">
       <c r="A42" s="16">
@@ -5434,12 +5547,8 @@
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
-      <c r="E42" s="16">
-        <v>15</v>
-      </c>
-      <c r="F42" s="16">
-        <v>5</v>
-      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
       <c r="A43" s="16">
@@ -5449,13 +5558,9 @@
         <v>15</v>
       </c>
       <c r="C43" s="16"/>
-      <c r="D43" s="16">
-        <v>10</v>
-      </c>
+      <c r="D43" s="16"/>
       <c r="E43" s="16"/>
-      <c r="F43" s="16">
-        <v>5</v>
-      </c>
+      <c r="F43" s="16"/>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1">
       <c r="A44" s="16">
@@ -5465,9 +5570,7 @@
         <v>10</v>
       </c>
       <c r="C44" s="16"/>
-      <c r="D44" s="16">
-        <v>10</v>
-      </c>
+      <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="52"/>
     </row>
@@ -5479,13 +5582,9 @@
         <v>20</v>
       </c>
       <c r="C45" s="16"/>
-      <c r="D45" s="16">
-        <v>10</v>
-      </c>
+      <c r="D45" s="16"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="16">
-        <v>10</v>
-      </c>
+      <c r="F45" s="16"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
       <c r="A46" s="16">
@@ -5496,9 +5595,7 @@
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
-      <c r="E46" s="16">
-        <v>15</v>
-      </c>
+      <c r="E46" s="16"/>
       <c r="F46" s="52"/>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1">
@@ -5510,9 +5607,7 @@
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
-      <c r="E47" s="16">
-        <v>15</v>
-      </c>
+      <c r="E47" s="16"/>
       <c r="F47" s="52"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
@@ -5524,9 +5619,7 @@
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
-      <c r="E48" s="16">
-        <v>20</v>
-      </c>
+      <c r="E48" s="16"/>
       <c r="F48" s="52"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1">
@@ -5538,9 +5631,7 @@
       </c>
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
-      <c r="E49" s="16">
-        <v>30</v>
-      </c>
+      <c r="E49" s="16"/>
       <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
@@ -5551,9 +5642,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="16"/>
-      <c r="D50" s="16">
-        <v>15</v>
-      </c>
+      <c r="D50" s="16"/>
       <c r="E50" s="16"/>
       <c r="F50" s="52"/>
     </row>
@@ -5567,13 +5656,9 @@
       <c r="C51" s="16">
         <v>15</v>
       </c>
-      <c r="D51" s="16">
-        <v>85</v>
-      </c>
+      <c r="D51" s="16"/>
       <c r="E51" s="16"/>
-      <c r="F51" s="16">
-        <v>80</v>
-      </c>
+      <c r="F51" s="16"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1">
       <c r="A52" s="16">
@@ -5598,9 +5683,7 @@
       </c>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
-      <c r="E53" s="16">
-        <v>15</v>
-      </c>
+      <c r="E53" s="16"/>
       <c r="F53" s="52"/>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
@@ -5611,9 +5694,7 @@
         <v>10</v>
       </c>
       <c r="C54" s="16"/>
-      <c r="D54" s="16">
-        <v>10</v>
-      </c>
+      <c r="D54" s="16"/>
       <c r="E54" s="16"/>
       <c r="F54" s="52"/>
     </row>
@@ -5625,9 +5706,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="16"/>
-      <c r="D55" s="16">
-        <v>10</v>
-      </c>
+      <c r="D55" s="16"/>
       <c r="E55" s="16"/>
       <c r="F55" s="52"/>
     </row>
@@ -5639,9 +5718,7 @@
         <v>15</v>
       </c>
       <c r="C56" s="16"/>
-      <c r="D56" s="16">
-        <v>15</v>
-      </c>
+      <c r="D56" s="16"/>
       <c r="E56" s="16"/>
       <c r="F56" s="52"/>
     </row>
@@ -5653,9 +5730,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="16"/>
-      <c r="D57" s="16">
-        <v>15</v>
-      </c>
+      <c r="D57" s="16"/>
       <c r="E57" s="16"/>
       <c r="F57" s="52"/>
     </row>
@@ -5667,9 +5742,7 @@
         <v>10</v>
       </c>
       <c r="C58" s="16"/>
-      <c r="D58" s="16">
-        <v>10</v>
-      </c>
+      <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="52"/>
     </row>
@@ -5681,9 +5754,7 @@
         <v>10</v>
       </c>
       <c r="C59" s="16"/>
-      <c r="D59" s="16">
-        <v>10</v>
-      </c>
+      <c r="D59" s="16"/>
       <c r="E59" s="16"/>
       <c r="F59" s="52"/>
     </row>
@@ -5695,9 +5766,7 @@
         <v>10</v>
       </c>
       <c r="C60" s="16"/>
-      <c r="D60" s="16">
-        <v>10</v>
-      </c>
+      <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="52"/>
     </row>
@@ -5709,13 +5778,9 @@
         <v>15</v>
       </c>
       <c r="C61" s="16"/>
-      <c r="D61" s="16">
-        <v>10</v>
-      </c>
+      <c r="D61" s="16"/>
       <c r="E61" s="16"/>
-      <c r="F61" s="16">
-        <v>5</v>
-      </c>
+      <c r="F61" s="16"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1">
       <c r="A62" s="16">
@@ -5725,13 +5790,9 @@
         <v>20</v>
       </c>
       <c r="C62" s="16"/>
-      <c r="D62" s="16">
-        <v>15</v>
-      </c>
+      <c r="D62" s="16"/>
       <c r="E62" s="16"/>
-      <c r="F62" s="16">
-        <v>5</v>
-      </c>
+      <c r="F62" s="16"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1">
       <c r="A63" s="16">
@@ -5742,12 +5803,8 @@
       </c>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
-      <c r="E63" s="16">
-        <v>10</v>
-      </c>
-      <c r="F63" s="16">
-        <v>5</v>
-      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
       <c r="A64" s="16">
@@ -5758,12 +5815,8 @@
       </c>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
-      <c r="E64" s="16">
-        <v>15</v>
-      </c>
-      <c r="F64" s="16">
-        <v>15</v>
-      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
       <c r="A65" s="16">
@@ -5774,12 +5827,8 @@
       </c>
       <c r="C65" s="52"/>
       <c r="D65" s="52"/>
-      <c r="E65" s="16">
-        <v>15</v>
-      </c>
-      <c r="F65" s="16">
-        <v>5</v>
-      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1">
       <c r="A66" s="16">
@@ -5790,9 +5839,7 @@
       </c>
       <c r="C66" s="52"/>
       <c r="D66" s="52"/>
-      <c r="E66" s="16">
-        <v>15</v>
-      </c>
+      <c r="E66" s="16"/>
       <c r="F66" s="52"/>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
@@ -5804,9 +5851,7 @@
       </c>
       <c r="C67" s="52"/>
       <c r="D67" s="52"/>
-      <c r="E67" s="16">
-        <v>10</v>
-      </c>
+      <c r="E67" s="16"/>
       <c r="F67" s="52"/>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
@@ -5818,12 +5863,8 @@
       </c>
       <c r="C68" s="52"/>
       <c r="D68" s="52"/>
-      <c r="E68" s="16">
-        <v>15</v>
-      </c>
-      <c r="F68" s="16">
-        <v>15</v>
-      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
       <c r="A69" s="16">
@@ -5835,9 +5876,7 @@
       <c r="C69" s="52"/>
       <c r="D69" s="52"/>
       <c r="E69" s="16"/>
-      <c r="F69" s="16">
-        <v>15</v>
-      </c>
+      <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
       <c r="A70" s="16">
@@ -5849,353 +5888,207 @@
       <c r="C70" s="52"/>
       <c r="D70" s="52"/>
       <c r="E70" s="16"/>
-      <c r="F70" s="16">
-        <v>15</v>
-      </c>
+      <c r="F70" s="16"/>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A71" s="16">
-        <v>70</v>
-      </c>
-      <c r="B71" s="16">
-        <v>10</v>
-      </c>
+      <c r="A71" s="16"/>
+      <c r="B71" s="16"/>
       <c r="C71" s="52"/>
       <c r="D71" s="52"/>
-      <c r="E71" s="16">
-        <v>10</v>
-      </c>
+      <c r="E71" s="16"/>
       <c r="F71" s="52"/>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A72" s="16">
-        <v>71</v>
-      </c>
-      <c r="B72" s="16">
-        <v>10</v>
-      </c>
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
       <c r="C72" s="52"/>
       <c r="D72" s="52"/>
-      <c r="E72" s="16">
-        <v>10</v>
-      </c>
+      <c r="E72" s="16"/>
       <c r="F72" s="52"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A73" s="16">
-        <v>72</v>
-      </c>
-      <c r="B73" s="16">
-        <v>20</v>
-      </c>
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
       <c r="C73" s="52"/>
       <c r="D73" s="52"/>
-      <c r="E73" s="16">
-        <v>15</v>
-      </c>
-      <c r="F73" s="16">
-        <v>5</v>
-      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A74" s="16">
-        <v>73</v>
-      </c>
-      <c r="B74" s="16">
-        <v>20</v>
-      </c>
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
       <c r="C74" s="52"/>
       <c r="D74" s="52"/>
       <c r="E74" s="16"/>
-      <c r="F74" s="16">
-        <v>20</v>
-      </c>
+      <c r="F74" s="16"/>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A75" s="16">
-        <v>74</v>
-      </c>
-      <c r="B75" s="16">
-        <v>15</v>
-      </c>
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
       <c r="C75" s="52"/>
       <c r="D75" s="52"/>
       <c r="E75" s="16"/>
-      <c r="F75" s="16">
-        <v>15</v>
-      </c>
+      <c r="F75" s="16"/>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A76" s="16">
-        <v>75</v>
-      </c>
-      <c r="B76" s="16">
-        <v>10</v>
-      </c>
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
       <c r="C76" s="52"/>
       <c r="D76" s="52"/>
-      <c r="E76" s="16">
-        <v>10</v>
-      </c>
+      <c r="E76" s="16"/>
       <c r="F76" s="52"/>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A77" s="16">
-        <v>76</v>
-      </c>
-      <c r="B77" s="16">
-        <v>20</v>
-      </c>
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
       <c r="C77" s="52"/>
       <c r="D77" s="52"/>
-      <c r="E77" s="16">
-        <v>15</v>
-      </c>
-      <c r="F77" s="16">
-        <v>5</v>
-      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A78" s="16">
-        <v>77</v>
-      </c>
-      <c r="B78" s="16">
-        <v>10</v>
-      </c>
+      <c r="A78" s="16"/>
+      <c r="B78" s="16"/>
       <c r="C78" s="52"/>
       <c r="D78" s="52"/>
-      <c r="E78" s="16">
-        <v>10</v>
-      </c>
+      <c r="E78" s="16"/>
       <c r="F78" s="52"/>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A79" s="16">
-        <v>78</v>
-      </c>
-      <c r="B79" s="16">
-        <v>30</v>
-      </c>
+      <c r="A79" s="16"/>
+      <c r="B79" s="16"/>
       <c r="C79" s="52"/>
       <c r="D79" s="52"/>
-      <c r="E79" s="16">
-        <v>20</v>
-      </c>
-      <c r="F79" s="16">
-        <v>10</v>
-      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A80" s="16">
-        <v>79</v>
-      </c>
-      <c r="B80" s="16">
-        <v>30</v>
-      </c>
+      <c r="A80" s="16"/>
+      <c r="B80" s="16"/>
       <c r="C80" s="52"/>
       <c r="D80" s="52"/>
       <c r="E80" s="16"/>
-      <c r="F80" s="16">
-        <v>30</v>
-      </c>
+      <c r="F80" s="16"/>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A81" s="16">
-        <v>80</v>
-      </c>
-      <c r="B81" s="16">
-        <v>10</v>
-      </c>
+      <c r="A81" s="16"/>
+      <c r="B81" s="16"/>
       <c r="C81" s="52"/>
       <c r="D81" s="52"/>
       <c r="E81" s="16"/>
       <c r="F81" s="16"/>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A82" s="16">
-        <v>81</v>
-      </c>
-      <c r="B82" s="16">
-        <v>15</v>
-      </c>
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
       <c r="C82" s="52"/>
       <c r="D82" s="52"/>
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A83" s="16">
-        <v>82</v>
-      </c>
-      <c r="B83" s="16">
-        <v>10</v>
-      </c>
+      <c r="A83" s="16"/>
+      <c r="B83" s="16"/>
       <c r="C83" s="52"/>
       <c r="D83" s="52"/>
       <c r="E83" s="52"/>
       <c r="F83" s="16"/>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A84" s="16">
-        <v>83</v>
-      </c>
-      <c r="B84" s="16">
-        <v>10</v>
-      </c>
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
       <c r="C84" s="52"/>
       <c r="D84" s="52"/>
       <c r="E84" s="52"/>
       <c r="F84" s="16"/>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A85" s="16">
-        <v>84</v>
-      </c>
-      <c r="B85" s="16">
-        <v>30</v>
-      </c>
+      <c r="A85" s="16"/>
+      <c r="B85" s="16"/>
       <c r="C85" s="52"/>
       <c r="D85" s="52"/>
       <c r="E85" s="52"/>
       <c r="F85" s="16"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A86" s="16">
-        <v>85</v>
-      </c>
-      <c r="B86" s="16">
-        <v>10</v>
-      </c>
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
       <c r="C86" s="52"/>
       <c r="D86" s="52"/>
       <c r="E86" s="52"/>
-      <c r="F86" s="16">
-        <v>10</v>
-      </c>
+      <c r="F86" s="16"/>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A87" s="16">
-        <v>86</v>
-      </c>
-      <c r="B87" s="16">
-        <v>25</v>
-      </c>
+      <c r="A87" s="16"/>
+      <c r="B87" s="16"/>
       <c r="C87" s="52"/>
       <c r="D87" s="52"/>
       <c r="E87" s="52"/>
-      <c r="F87" s="16">
-        <v>25</v>
-      </c>
+      <c r="F87" s="16"/>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A88" s="16">
-        <v>87</v>
-      </c>
-      <c r="B88" s="16">
-        <v>15</v>
-      </c>
+      <c r="A88" s="16"/>
+      <c r="B88" s="16"/>
       <c r="C88" s="52"/>
       <c r="D88" s="52"/>
       <c r="E88" s="52"/>
-      <c r="F88" s="16">
-        <v>15</v>
-      </c>
+      <c r="F88" s="16"/>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A89" s="16">
-        <v>88</v>
-      </c>
-      <c r="B89" s="16">
-        <v>10</v>
-      </c>
+      <c r="A89" s="16"/>
+      <c r="B89" s="16"/>
       <c r="C89" s="52"/>
       <c r="D89" s="52"/>
       <c r="E89" s="52"/>
-      <c r="F89" s="16">
-        <v>10</v>
-      </c>
+      <c r="F89" s="16"/>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A90" s="16">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16">
-        <v>20</v>
-      </c>
+      <c r="A90" s="16"/>
+      <c r="B90" s="16"/>
       <c r="C90" s="52"/>
       <c r="D90" s="52"/>
       <c r="E90" s="52"/>
       <c r="F90" s="16"/>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A91" s="16">
-        <v>90</v>
-      </c>
-      <c r="B91" s="16">
-        <v>15</v>
-      </c>
+      <c r="A91" s="16"/>
+      <c r="B91" s="16"/>
       <c r="C91" s="52"/>
       <c r="D91" s="52"/>
       <c r="E91" s="52"/>
-      <c r="F91" s="16">
-        <v>15</v>
-      </c>
+      <c r="F91" s="16"/>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A92" s="16">
-        <v>91</v>
-      </c>
-      <c r="B92" s="16">
-        <v>20</v>
-      </c>
+      <c r="A92" s="16"/>
+      <c r="B92" s="16"/>
       <c r="C92" s="52"/>
       <c r="D92" s="52"/>
       <c r="E92" s="52"/>
-      <c r="F92" s="16">
-        <v>20</v>
-      </c>
+      <c r="F92" s="16"/>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A93" s="16">
-        <v>92</v>
-      </c>
-      <c r="B93" s="16">
-        <v>20</v>
-      </c>
+      <c r="A93" s="16"/>
+      <c r="B93" s="16"/>
       <c r="C93" s="52"/>
       <c r="D93" s="52"/>
       <c r="E93" s="52"/>
-      <c r="F93" s="16">
-        <v>20</v>
-      </c>
+      <c r="F93" s="16"/>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A94" s="16">
-        <v>93</v>
-      </c>
-      <c r="B94" s="16">
-        <v>20</v>
-      </c>
+      <c r="A94" s="16"/>
+      <c r="B94" s="16"/>
       <c r="C94" s="52"/>
       <c r="D94" s="52"/>
       <c r="E94" s="52"/>
-      <c r="F94" s="16">
-        <v>20</v>
-      </c>
+      <c r="F94" s="16"/>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A95" s="16">
-        <v>94</v>
-      </c>
-      <c r="B95" s="16">
-        <v>20</v>
-      </c>
+      <c r="A95" s="16"/>
+      <c r="B95" s="16"/>
       <c r="C95" s="52"/>
       <c r="D95" s="52"/>
       <c r="E95" s="52"/>
-      <c r="F95" s="16">
-        <v>20</v>
-      </c>
+      <c r="F95" s="16"/>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1">
       <c r="D96" s="52"/>

--- a/TodoList.xlsx
+++ b/TodoList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mikajy\Documents\GitHub\Mini-Projet-Web-Mars2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8C48B9-5CFA-4296-B618-191CA9716182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F1BED-A29F-4F4E-BD69-1E7641DF732A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TodoList.xlsx
+++ b/TodoList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mikajy\Documents\GitHub\Mini-Projet-Web-Mars2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8C48B9-5CFA-4296-B618-191CA9716182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B18D40-54BD-432E-B39D-50ACC81D1FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="91">
   <si>
     <t>Ligne</t>
   </si>
@@ -305,6 +305,15 @@
   </si>
   <si>
     <t>Ajouter navigation cohérente</t>
+  </si>
+  <si>
+    <t>categorie_add</t>
+  </si>
+  <si>
+    <t>Formulaire categorie</t>
+  </si>
+  <si>
+    <t>categorie_edit</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Mikajy" refreshedDate="46111.832195833333" refreshedVersion="7" recordCount="112" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Mikajy" refreshedDate="46112.468149768516" refreshedVersion="7" recordCount="112" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="B1:K919" sheet="liste des taches"/>
   </cacheSource>
@@ -2101,7 +2110,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Recap" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0">
   <location ref="A1:D6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField name="Catégorie" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -2507,11 +2516,11 @@
         <v>20</v>
       </c>
       <c r="J2" s="5">
-        <f t="shared" ref="J2:J45" si="0">H2-I2</f>
+        <f t="shared" ref="J2:J35" si="0">H2-I2</f>
         <v>0</v>
       </c>
       <c r="K2" s="6">
-        <f t="shared" ref="K2:K45" si="1">(I2/(I2+J2))</f>
+        <f t="shared" ref="K2:K35" si="1">(I2/(I2+J2))</f>
         <v>1</v>
       </c>
     </row>
@@ -3552,84 +3561,148 @@
       <c r="A31" s="45">
         <v>30</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="49"/>
+      <c r="B31" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="47">
+        <v>5</v>
+      </c>
+      <c r="I31" s="49">
+        <v>5</v>
+      </c>
       <c r="J31" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K31" s="6" t="e">
+      <c r="K31" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="45">
         <v>31</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="49"/>
+      <c r="B32" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="47">
+        <v>5</v>
+      </c>
+      <c r="I32" s="49">
+        <v>5</v>
+      </c>
       <c r="J32" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K32" s="6" t="e">
+      <c r="K32" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="45">
         <v>32</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="49"/>
+      <c r="B33" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="47">
+        <v>5</v>
+      </c>
+      <c r="I33" s="49">
+        <v>5</v>
+      </c>
       <c r="J33" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K33" s="6" t="e">
+      <c r="K33" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="45">
         <v>33</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="49"/>
+      <c r="B34" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="47">
+        <v>5</v>
+      </c>
+      <c r="I34" s="49">
+        <v>5</v>
+      </c>
       <c r="J34" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K34" s="6" t="e">
+      <c r="K34" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1">
@@ -4946,11 +5019,11 @@
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="11">
         <f>SUM('liste des taches'!H:H)</f>
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="B2" s="11">
         <f>SUM('liste des taches'!I:I)</f>
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="C2" s="11">
         <f>SUM('liste des taches'!J:J)</f>
@@ -5000,7 +5073,9 @@
       <c r="C1" s="15">
         <v>46111</v>
       </c>
-      <c r="D1" s="15"/>
+      <c r="D1" s="15">
+        <v>46112</v>
+      </c>
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
@@ -5414,9 +5489,13 @@
       <c r="A31" s="16">
         <v>30</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="16">
+        <v>5</v>
+      </c>
       <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="D31" s="16">
+        <v>5</v>
+      </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
     </row>
@@ -5424,9 +5503,13 @@
       <c r="A32" s="16">
         <v>31</v>
       </c>
-      <c r="B32" s="16"/>
+      <c r="B32" s="16">
+        <v>5</v>
+      </c>
       <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
+      <c r="D32" s="16">
+        <v>5</v>
+      </c>
       <c r="E32" s="16"/>
       <c r="F32" s="16"/>
     </row>
@@ -5434,9 +5517,13 @@
       <c r="A33" s="16">
         <v>32</v>
       </c>
-      <c r="B33" s="16"/>
+      <c r="B33" s="16">
+        <v>5</v>
+      </c>
       <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
+      <c r="D33" s="16">
+        <v>5</v>
+      </c>
       <c r="E33" s="16"/>
       <c r="F33" s="16"/>
     </row>
@@ -5444,11 +5531,13 @@
       <c r="A34" s="16">
         <v>33</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16">
-        <v>10</v>
-      </c>
-      <c r="D34" s="16"/>
+      <c r="B34" s="16">
+        <v>5</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16">
+        <v>5</v>
+      </c>
       <c r="E34" s="16"/>
       <c r="F34" s="16"/>
     </row>
@@ -5456,12 +5545,8 @@
       <c r="A35" s="16">
         <v>34</v>
       </c>
-      <c r="B35" s="16">
-        <v>15</v>
-      </c>
-      <c r="C35" s="16">
-        <v>15</v>
-      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="16"/>
@@ -5470,9 +5555,7 @@
       <c r="A36" s="16">
         <v>35</v>
       </c>
-      <c r="B36" s="16">
-        <v>10</v>
-      </c>
+      <c r="B36" s="16"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
@@ -5482,9 +5565,7 @@
       <c r="A37" s="16">
         <v>36</v>
       </c>
-      <c r="B37" s="16">
-        <v>10</v>
-      </c>
+      <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
@@ -5494,9 +5575,7 @@
       <c r="A38" s="16">
         <v>37</v>
       </c>
-      <c r="B38" s="16">
-        <v>15</v>
-      </c>
+      <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
@@ -5506,9 +5585,7 @@
       <c r="A39" s="16">
         <v>38</v>
       </c>
-      <c r="B39" s="16">
-        <v>20</v>
-      </c>
+      <c r="B39" s="16"/>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
@@ -5518,9 +5595,7 @@
       <c r="A40" s="16">
         <v>39</v>
       </c>
-      <c r="B40" s="16">
-        <v>10</v>
-      </c>
+      <c r="B40" s="16"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
@@ -5530,9 +5605,7 @@
       <c r="A41" s="16">
         <v>40</v>
       </c>
-      <c r="B41" s="16">
-        <v>25</v>
-      </c>
+      <c r="B41" s="16"/>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
@@ -5542,9 +5615,7 @@
       <c r="A42" s="16">
         <v>41</v>
       </c>
-      <c r="B42" s="16">
-        <v>20</v>
-      </c>
+      <c r="B42" s="16"/>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
@@ -5554,9 +5625,7 @@
       <c r="A43" s="16">
         <v>42</v>
       </c>
-      <c r="B43" s="16">
-        <v>15</v>
-      </c>
+      <c r="B43" s="16"/>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -5566,9 +5635,7 @@
       <c r="A44" s="16">
         <v>43</v>
       </c>
-      <c r="B44" s="16">
-        <v>10</v>
-      </c>
+      <c r="B44" s="16"/>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -5578,9 +5645,7 @@
       <c r="A45" s="16">
         <v>44</v>
       </c>
-      <c r="B45" s="16">
-        <v>20</v>
-      </c>
+      <c r="B45" s="16"/>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -5590,9 +5655,7 @@
       <c r="A46" s="16">
         <v>45</v>
       </c>
-      <c r="B46" s="16">
-        <v>15</v>
-      </c>
+      <c r="B46" s="16"/>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -5602,9 +5665,7 @@
       <c r="A47" s="16">
         <v>46</v>
       </c>
-      <c r="B47" s="16">
-        <v>15</v>
-      </c>
+      <c r="B47" s="16"/>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
@@ -5614,9 +5675,7 @@
       <c r="A48" s="16">
         <v>47</v>
       </c>
-      <c r="B48" s="16">
-        <v>20</v>
-      </c>
+      <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
@@ -5626,265 +5685,175 @@
       <c r="A49" s="16">
         <v>48</v>
       </c>
-      <c r="B49" s="16">
-        <v>30</v>
-      </c>
+      <c r="B49" s="16"/>
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
       <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A50" s="16">
-        <v>49</v>
-      </c>
-      <c r="B50" s="16">
-        <v>15</v>
-      </c>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
       <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A51" s="16">
-        <v>50</v>
-      </c>
-      <c r="B51" s="16">
-        <v>180</v>
-      </c>
-      <c r="C51" s="16">
-        <v>15</v>
-      </c>
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
       <c r="F51" s="16"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A52" s="16">
-        <v>51</v>
-      </c>
-      <c r="B52" s="16">
-        <v>15</v>
-      </c>
-      <c r="C52" s="16">
-        <v>15</v>
-      </c>
+      <c r="A52" s="16"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
       <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A53" s="16">
-        <v>52</v>
-      </c>
-      <c r="B53" s="16">
-        <v>15</v>
-      </c>
+      <c r="A53" s="16"/>
+      <c r="B53" s="16"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
       <c r="F53" s="52"/>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A54" s="16">
-        <v>53</v>
-      </c>
-      <c r="B54" s="16">
-        <v>10</v>
-      </c>
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
       <c r="F54" s="52"/>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A55" s="16">
-        <v>54</v>
-      </c>
-      <c r="B55" s="16">
-        <v>10</v>
-      </c>
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
       <c r="F55" s="52"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A56" s="16">
-        <v>55</v>
-      </c>
-      <c r="B56" s="16">
-        <v>15</v>
-      </c>
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
       <c r="F56" s="52"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A57" s="16">
-        <v>56</v>
-      </c>
-      <c r="B57" s="16">
-        <v>15</v>
-      </c>
+      <c r="A57" s="16"/>
+      <c r="B57" s="16"/>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
       <c r="F57" s="52"/>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A58" s="16">
-        <v>57</v>
-      </c>
-      <c r="B58" s="16">
-        <v>10</v>
-      </c>
+      <c r="A58" s="16"/>
+      <c r="B58" s="16"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="52"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A59" s="16">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16">
-        <v>10</v>
-      </c>
+      <c r="A59" s="16"/>
+      <c r="B59" s="16"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
       <c r="F59" s="52"/>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A60" s="16">
-        <v>59</v>
-      </c>
-      <c r="B60" s="16">
-        <v>10</v>
-      </c>
+      <c r="A60" s="16"/>
+      <c r="B60" s="16"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="52"/>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A61" s="16">
-        <v>60</v>
-      </c>
-      <c r="B61" s="16">
-        <v>15</v>
-      </c>
+      <c r="A61" s="16"/>
+      <c r="B61" s="16"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A62" s="16">
-        <v>61</v>
-      </c>
-      <c r="B62" s="16">
-        <v>20</v>
-      </c>
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A63" s="16">
-        <v>62</v>
-      </c>
-      <c r="B63" s="16">
-        <v>15</v>
-      </c>
+      <c r="A63" s="16"/>
+      <c r="B63" s="16"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A64" s="16">
-        <v>63</v>
-      </c>
-      <c r="B64" s="16">
-        <v>30</v>
-      </c>
+      <c r="A64" s="16"/>
+      <c r="B64" s="16"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
       <c r="F64" s="16"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A65" s="16">
-        <v>64</v>
-      </c>
-      <c r="B65" s="16">
-        <v>20</v>
-      </c>
+      <c r="A65" s="16"/>
+      <c r="B65" s="16"/>
       <c r="C65" s="52"/>
       <c r="D65" s="52"/>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A66" s="16">
-        <v>65</v>
-      </c>
-      <c r="B66" s="16">
-        <v>15</v>
-      </c>
+      <c r="A66" s="16"/>
+      <c r="B66" s="16"/>
       <c r="C66" s="52"/>
       <c r="D66" s="52"/>
       <c r="E66" s="16"/>
       <c r="F66" s="52"/>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A67" s="16">
-        <v>66</v>
-      </c>
-      <c r="B67" s="16">
-        <v>10</v>
-      </c>
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
       <c r="C67" s="52"/>
       <c r="D67" s="52"/>
       <c r="E67" s="16"/>
       <c r="F67" s="52"/>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A68" s="16">
-        <v>67</v>
-      </c>
-      <c r="B68" s="16">
-        <v>30</v>
-      </c>
+      <c r="A68" s="16"/>
+      <c r="B68" s="16"/>
       <c r="C68" s="52"/>
       <c r="D68" s="52"/>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A69" s="16">
-        <v>68</v>
-      </c>
-      <c r="B69" s="16">
-        <v>15</v>
-      </c>
+      <c r="A69" s="16"/>
+      <c r="B69" s="16"/>
       <c r="C69" s="52"/>
       <c r="D69" s="52"/>
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A70" s="16">
-        <v>69</v>
-      </c>
-      <c r="B70" s="16">
-        <v>15</v>
-      </c>
+      <c r="A70" s="16"/>
+      <c r="B70" s="16"/>
       <c r="C70" s="52"/>
       <c r="D70" s="52"/>
       <c r="E70" s="16"/>
